--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_coquimbo.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2019_coquimbo.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>29.27781437923155</v>
+      </c>
+      <c r="C2">
         <v>26.13717601872748</v>
-      </c>
-      <c r="C2">
-        <v>29.27781437923155</v>
       </c>
       <c r="D2">
         <v>3.825968036039901</v>
       </c>
       <c r="E2">
-        <v>16.81766729953144</v>
+        <v>18.83847517170779</v>
       </c>
       <c r="F2">
         <v>64.34385752876078</v>
       </c>
       <c r="G2">
-        <v>18.83847517170779</v>
+        <v>16.81766729953144</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>29.67932976097141</v>
+      </c>
+      <c r="C3">
         <v>25.32446074397569</v>
-      </c>
-      <c r="C3">
-        <v>29.67932976097141</v>
       </c>
       <c r="D3">
         <v>3.948751407225463</v>
       </c>
       <c r="E3">
-        <v>16.33796222755432</v>
+        <v>19.14748643519409</v>
       </c>
       <c r="F3">
         <v>64.51455133725159</v>
       </c>
       <c r="G3">
-        <v>19.14748643519409</v>
+        <v>16.33796222755432</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>32.63353707148552</v>
+      </c>
+      <c r="C4">
         <v>31.75657719904332</v>
-      </c>
-      <c r="C4">
-        <v>32.63353707148552</v>
       </c>
       <c r="D4">
         <v>3.148953974895397</v>
       </c>
       <c r="E4">
-        <v>19.31781441965729</v>
+        <v>19.85127707727126</v>
       </c>
       <c r="F4">
         <v>60.83090850307145</v>
       </c>
       <c r="G4">
-        <v>19.85127707727126</v>
+        <v>19.31781441965729</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>44.98787388843977</v>
+      </c>
+      <c r="C5">
         <v>32.821341956346</v>
-      </c>
-      <c r="C5">
-        <v>44.98787388843977</v>
       </c>
       <c r="D5">
         <v>3.04679802955665</v>
       </c>
       <c r="E5">
-        <v>18.45874062286884</v>
+        <v>25.30120481927711</v>
       </c>
       <c r="F5">
         <v>56.24005455785406</v>
       </c>
       <c r="G5">
-        <v>25.30120481927711</v>
+        <v>18.45874062286884</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>30.48302872062663</v>
+      </c>
+      <c r="C6">
         <v>32.04960835509139</v>
-      </c>
-      <c r="C6">
-        <v>30.48302872062663</v>
       </c>
       <c r="D6">
         <v>3.120162932790224</v>
       </c>
       <c r="E6">
-        <v>19.71887550200803</v>
+        <v>18.75502008032128</v>
       </c>
       <c r="F6">
         <v>61.52610441767068</v>
       </c>
       <c r="G6">
-        <v>18.75502008032128</v>
+        <v>19.71887550200803</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>27.96579611600474</v>
+      </c>
+      <c r="C7">
         <v>28.18214598464946</v>
-      </c>
-      <c r="C7">
-        <v>27.96579611600474</v>
       </c>
       <c r="D7">
         <v>3.548345823432645</v>
       </c>
       <c r="E7">
+        <v>17.90980767327549</v>
+      </c>
+      <c r="F7">
+        <v>64.04183023785174</v>
+      </c>
+      <c r="G7">
         <v>18.04836208887276</v>
-      </c>
-      <c r="F7">
-        <v>64.04183023785176</v>
-      </c>
-      <c r="G7">
-        <v>17.90980767327549</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>30.02521089886551</v>
+      </c>
+      <c r="C8">
         <v>31.91602831377873</v>
-      </c>
-      <c r="C8">
-        <v>30.02521089886551</v>
       </c>
       <c r="D8">
         <v>3.133221935287863</v>
       </c>
       <c r="E8">
-        <v>19.70840069456919</v>
+        <v>18.54080593976409</v>
       </c>
       <c r="F8">
         <v>61.75079336566673</v>
       </c>
       <c r="G8">
-        <v>18.54080593976409</v>
+        <v>19.70840069456919</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.55601659751037</v>
+      </c>
+      <c r="C9">
         <v>47.55186721991701</v>
-      </c>
-      <c r="C9">
-        <v>31.55601659751037</v>
       </c>
       <c r="D9">
         <v>2.102966841186737</v>
       </c>
       <c r="E9">
-        <v>26.54928761728252</v>
+        <v>17.61844086644272</v>
       </c>
       <c r="F9">
         <v>55.83227151627477</v>
       </c>
       <c r="G9">
-        <v>17.61844086644272</v>
+        <v>26.54928761728252</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.56455309396486</v>
+      </c>
+      <c r="C10">
         <v>31.16883116883117</v>
-      </c>
-      <c r="C10">
-        <v>29.56455309396486</v>
       </c>
       <c r="D10">
         <v>3.208333333333333</v>
       </c>
       <c r="E10">
-        <v>19.3916349809886</v>
+        <v>18.393536121673</v>
       </c>
       <c r="F10">
         <v>62.21482889733841</v>
       </c>
       <c r="G10">
-        <v>18.393536121673</v>
+        <v>19.3916349809886</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>29.4435261707989</v>
+      </c>
+      <c r="C11">
         <v>29.64187327823691</v>
-      </c>
-      <c r="C11">
-        <v>29.4435261707989</v>
       </c>
       <c r="D11">
         <v>3.37360594795539</v>
       </c>
       <c r="E11">
-        <v>18.6326799196509</v>
+        <v>18.50800027706588</v>
       </c>
       <c r="F11">
         <v>62.85931980328323</v>
       </c>
       <c r="G11">
-        <v>18.50800027706588</v>
+        <v>18.6326799196509</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>29.45592277084216</v>
+      </c>
+      <c r="C12">
         <v>28.15828695664064</v>
-      </c>
-      <c r="C12">
-        <v>29.45592277084216</v>
       </c>
       <c r="D12">
         <v>3.551352401301413</v>
       </c>
       <c r="E12">
-        <v>17.86532255265989</v>
+        <v>18.68862129992712</v>
       </c>
       <c r="F12">
         <v>63.44605614741299</v>
       </c>
       <c r="G12">
-        <v>18.68862129992712</v>
+        <v>17.86532255265989</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>26.35773653649095</v>
+      </c>
+      <c r="C13">
         <v>40.86303085506091</v>
-      </c>
-      <c r="C13">
-        <v>26.35773653649095</v>
       </c>
       <c r="D13">
         <v>2.447199777096684</v>
       </c>
       <c r="E13">
-        <v>24.43657656430857</v>
+        <v>15.76223871450943</v>
       </c>
       <c r="F13">
         <v>59.80118472118199</v>
       </c>
       <c r="G13">
-        <v>15.76223871450943</v>
+        <v>24.43657656430857</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>30.11632041448672</v>
+      </c>
+      <c r="C14">
         <v>29.9334586275207</v>
-      </c>
-      <c r="C14">
-        <v>30.11632041448672</v>
       </c>
       <c r="D14">
         <v>3.340743254708977</v>
       </c>
       <c r="E14">
-        <v>18.70259290996223</v>
+        <v>18.8168459805135</v>
       </c>
       <c r="F14">
         <v>62.48056110952426</v>
       </c>
       <c r="G14">
-        <v>18.8168459805135</v>
+        <v>18.70259290996223</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>29.56632653061225</v>
+      </c>
+      <c r="C15">
         <v>34.17091836734694</v>
-      </c>
-      <c r="C15">
-        <v>29.56632653061225</v>
       </c>
       <c r="D15">
         <v>2.926465098917507</v>
       </c>
       <c r="E15">
-        <v>20.8693620004674</v>
+        <v>18.05717846848952</v>
       </c>
       <c r="F15">
         <v>61.07345953104308</v>
       </c>
       <c r="G15">
-        <v>18.05717846848952</v>
+        <v>20.8693620004674</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>26.03907637655418</v>
+      </c>
+      <c r="C16">
         <v>44.26287744227353</v>
-      </c>
-      <c r="C16">
-        <v>26.03907637655418</v>
       </c>
       <c r="D16">
         <v>2.259229534510433</v>
       </c>
       <c r="E16">
-        <v>25.99082186065916</v>
+        <v>15.28994576554026</v>
       </c>
       <c r="F16">
         <v>58.71923237380058</v>
       </c>
       <c r="G16">
-        <v>15.28994576554026</v>
+        <v>25.99082186065916</v>
       </c>
     </row>
   </sheetData>
